--- a/static/contracts/_normalized_template.xlsx
+++ b/static/contracts/_normalized_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gyl\Supply_chain_agent\Supply_chain_agent\static\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94ADFFDB-E1E2-4895-A824-6FCF53F4BE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF079B02-F1D3-417F-82F5-9E0D0294D06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14916" yWindow="732" windowWidth="8124" windowHeight="11508" xr2:uid="{E646507C-A6FE-4872-A16F-EE1AADB13FE7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E646507C-A6FE-4872-A16F-EE1AADB13FE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>

--- a/static/contracts/_normalized_template.xlsx
+++ b/static/contracts/_normalized_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gyl\Supply_chain_agent\Supply_chain_agent\static\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF079B02-F1D3-417F-82F5-9E0D0294D06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D4037DB-BBE0-468C-8812-9642F1EEC287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E646507C-A6FE-4872-A16F-EE1AADB13FE7}"/>
   </bookViews>

--- a/static/contracts/_normalized_template.xlsx
+++ b/static/contracts/_normalized_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gyl\Supply_chain_agent\Supply_chain_agent\static\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D4037DB-BBE0-468C-8812-9642F1EEC287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF99AB8-4C12-4A37-A7B6-7D60126147AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E646507C-A6FE-4872-A16F-EE1AADB13FE7}"/>
   </bookViews>

--- a/static/contracts/_normalized_template.xlsx
+++ b/static/contracts/_normalized_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gyl\Supply_chain_agent\Supply_chain_agent\static\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF99AB8-4C12-4A37-A7B6-7D60126147AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA30AE5C-58CF-4C74-A039-60171A818CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E646507C-A6FE-4872-A16F-EE1AADB13FE7}"/>
   </bookViews>

--- a/static/contracts/_normalized_template.xlsx
+++ b/static/contracts/_normalized_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gyl\Supply_chain_agent\Supply_chain_agent\static\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA30AE5C-58CF-4C74-A039-60171A818CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{544D7CFB-170B-4E00-8B2D-32F360CFE089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E646507C-A6FE-4872-A16F-EE1AADB13FE7}"/>
   </bookViews>

--- a/static/contracts/_normalized_template.xlsx
+++ b/static/contracts/_normalized_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gyl\Supply_chain_agent\Supply_chain_agent\static\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{544D7CFB-170B-4E00-8B2D-32F360CFE089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE598F85-D7A2-438F-B3CE-FE185509CA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E646507C-A6FE-4872-A16F-EE1AADB13FE7}"/>
   </bookViews>
